--- a/results/regression_output/pre_covid_analysis/extended_control_specifications.xlsx
+++ b/results/regression_output/pre_covid_analysis/extended_control_specifications.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,76 +413,86 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>specification</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>controls</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>n_controls</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>eu_elasticity</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>eu_se</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>eu_pval</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>eap_elasticity</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>eap_se</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>eap_pval</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>interaction_coef</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>interaction_pval</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>gdp_coef</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>gdp_pval</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>n_obs</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>r_squared</t>
         </is>
@@ -520,34 +518,40 @@
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1154315327473595</v>
+        <v>-0.1012746800182214</v>
       </c>
       <c r="F2" t="n">
-        <v>0.05483296800165784</v>
+        <v>0.05275385897832816</v>
       </c>
       <c r="G2" t="n">
-        <v>0.03618212557027589</v>
+        <v>0.05591911331221899</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.6091572353765753</v>
+        <v>-0.5950760110920712</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07711514409552492</v>
+        <v>0.07595852059371849</v>
       </c>
       <c r="J2" t="n">
-        <v>6.683542608243442e-14</v>
+        <v>1.023625628704394e-13</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.4937257026292158</v>
+        <v>-0.4938013310738498</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>0.2302729821350686</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0004730741683796058</v>
+      </c>
+      <c r="O2" t="n">
         <v>330</v>
       </c>
-      <c r="N2" t="n">
-        <v>0.4077433673083014</v>
+      <c r="P2" t="n">
+        <v>0.403069015694194</v>
       </c>
     </row>
     <row r="3">
@@ -570,34 +574,40 @@
         <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1158825156151602</v>
+        <v>-0.1013087820410415</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05543155839011415</v>
+        <v>0.05423975866894883</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0374667862375635</v>
+        <v>0.06283138137427047</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.5869033239689503</v>
+        <v>-0.5701733674122083</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0873322900666722</v>
+        <v>0.08462373399190269</v>
       </c>
       <c r="J3" t="n">
-        <v>1.007165462141302e-10</v>
+        <v>9.086242869216221e-11</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4710208083537901</v>
+        <v>-0.4688645853711668</v>
       </c>
       <c r="L3" t="n">
-        <v>2.131939069727196e-11</v>
+        <v>4.932942943014496e-12</v>
       </c>
       <c r="M3" t="n">
+        <v>0.2075323848380285</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.003188053329227003</v>
+      </c>
+      <c r="O3" t="n">
         <v>330</v>
       </c>
-      <c r="N3" t="n">
-        <v>0.3687322681732338</v>
+      <c r="P3" t="n">
+        <v>0.3637789415331618</v>
       </c>
     </row>
     <row r="4">
@@ -620,34 +630,40 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1649218012390685</v>
+        <v>-0.1422961552191508</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04150671860181034</v>
+        <v>0.04164735291690167</v>
       </c>
       <c r="G4" t="n">
-        <v>8.998202282950452e-05</v>
+        <v>0.0007268483647278057</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6291249223600274</v>
+        <v>-0.6184671711737429</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06165217011677911</v>
+        <v>0.06144700679653801</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4642031211209589</v>
+        <v>-0.4761710159545921</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
+        <v>0.2184355659499587</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.001035078221645058</v>
+      </c>
+      <c r="O4" t="n">
         <v>330</v>
       </c>
-      <c r="N4" t="n">
-        <v>0.3515984955856093</v>
+      <c r="P4" t="n">
+        <v>0.3369701883695086</v>
       </c>
     </row>
     <row r="5">
@@ -670,34 +686,40 @@
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.08907357686081817</v>
+        <v>-0.08958684331528761</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04334966613875779</v>
+        <v>0.04336494073981145</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04081596912934504</v>
+        <v>0.03974645259266163</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6042160088263714</v>
+        <v>-0.6038543099674142</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08650774548644204</v>
+        <v>0.08660433020564759</v>
       </c>
       <c r="J5" t="n">
-        <v>2.030531298657934e-11</v>
+        <v>2.18360884929325e-11</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5151424319655532</v>
+        <v>-0.5142674666521265</v>
       </c>
       <c r="L5" t="n">
-        <v>3.793498848381205e-11</v>
+        <v>4.30653290806049e-11</v>
       </c>
       <c r="M5" t="n">
+        <v>0.1808059785361909</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.006837393043948037</v>
+      </c>
+      <c r="O5" t="n">
         <v>330</v>
       </c>
-      <c r="N5" t="n">
-        <v>0.2778786084066538</v>
+      <c r="P5" t="n">
+        <v>0.2774644207172029</v>
       </c>
     </row>
     <row r="6">
@@ -720,34 +742,40 @@
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.03256979643026289</v>
+        <v>-0.03323752408890467</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07450538763465613</v>
+        <v>0.07440104400984482</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6623382286701092</v>
+        <v>0.655408332119124</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5964395374090085</v>
+        <v>-0.5960227390393019</v>
       </c>
       <c r="I6" t="n">
-        <v>0.116572086080338</v>
+        <v>0.1165329424726069</v>
       </c>
       <c r="J6" t="n">
-        <v>5.7520500829078e-07</v>
+        <v>5.804106248952223e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5638697409787455</v>
+        <v>-0.5627852149503972</v>
       </c>
       <c r="L6" t="n">
-        <v>1.205781474666878e-09</v>
+        <v>1.309377495317676e-09</v>
       </c>
       <c r="M6" t="n">
+        <v>0.1996436795780761</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.006810189278386058</v>
+      </c>
+      <c r="O6" t="n">
         <v>330</v>
       </c>
-      <c r="N6" t="n">
-        <v>0.29600268868056</v>
+      <c r="P6" t="n">
+        <v>0.2955499435836599</v>
       </c>
     </row>
     <row r="7">
@@ -770,34 +798,40 @@
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1398502643201729</v>
+        <v>-0.1042039704432872</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02814002330474057</v>
+        <v>0.027955789074258</v>
       </c>
       <c r="G7" t="n">
-        <v>1.164555711419268e-06</v>
+        <v>0.0002337105161123176</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6358142906140419</v>
+        <v>-0.6214122143746015</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05900787281843666</v>
+        <v>0.0593553884283942</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.495964026293869</v>
+        <v>-0.5172082439313143</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
+        <v>0.2083612471313943</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.004818185390950802</v>
+      </c>
+      <c r="O7" t="n">
         <v>330</v>
       </c>
-      <c r="N7" t="n">
-        <v>0.2983535096610027</v>
+      <c r="P7" t="n">
+        <v>0.2770951802582408</v>
       </c>
     </row>
     <row r="8">
@@ -820,34 +854,40 @@
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0936415282249617</v>
+        <v>-0.09423942220541649</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03971181078050009</v>
+        <v>0.03982449669822309</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01905272688766191</v>
+        <v>0.01863714556317131</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6312092142183778</v>
+        <v>-0.6308449359973219</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06549614167284182</v>
+        <v>0.0656358092886765</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5375676859934161</v>
+        <v>-0.5366055137919055</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
+        <v>0.1441191863219968</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.009090106436490775</v>
+      </c>
+      <c r="O8" t="n">
         <v>330</v>
       </c>
-      <c r="N8" t="n">
-        <v>0.3012598309583548</v>
+      <c r="P8" t="n">
+        <v>0.3009180083040703</v>
       </c>
     </row>
     <row r="9">
@@ -870,34 +910,40 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.08139397123409917</v>
+        <v>-0.08194043458782239</v>
       </c>
       <c r="F9" t="n">
-        <v>0.04169927565867901</v>
+        <v>0.04169188303671995</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05192596311908515</v>
+        <v>0.05034106042070841</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6154347561486616</v>
+        <v>-0.6150393409074353</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08612396986985485</v>
+        <v>0.08619240858568283</v>
       </c>
       <c r="J9" t="n">
-        <v>7.506661958700533e-12</v>
+        <v>7.997380535584853e-12</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5340407849145624</v>
+        <v>-0.5330989063196129</v>
       </c>
       <c r="L9" t="n">
-        <v>1.079492051303532e-11</v>
+        <v>1.222000278744417e-11</v>
       </c>
       <c r="M9" t="n">
+        <v>0.1867231519935794</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.007412286957614311</v>
+      </c>
+      <c r="O9" t="n">
         <v>330</v>
       </c>
-      <c r="N9" t="n">
-        <v>0.274471895349625</v>
+      <c r="P9" t="n">
+        <v>0.2740896489927416</v>
       </c>
     </row>
   </sheetData>

--- a/results/regression_output/pre_covid_analysis/extended_control_specifications.xlsx
+++ b/results/regression_output/pre_covid_analysis/extended_control_specifications.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,6 +497,11 @@
           <t>r_squared</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>df_resid</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -530,10 +535,10 @@
         <v>-0.5950760110920712</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07595852059371849</v>
+        <v>0.06080434296142236</v>
       </c>
       <c r="J2" t="n">
-        <v>1.023625628704394e-13</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>-0.4938013310738498</v>
@@ -552,6 +557,9 @@
       </c>
       <c r="P2" t="n">
         <v>0.403069015694194</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>276</v>
       </c>
     </row>
     <row r="3">
@@ -586,10 +594,10 @@
         <v>-0.5701733674122083</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08462373399190269</v>
+        <v>0.07424701915835026</v>
       </c>
       <c r="J3" t="n">
-        <v>9.086242869216221e-11</v>
+        <v>2.664535259100376e-13</v>
       </c>
       <c r="K3" t="n">
         <v>-0.4688645853711668</v>
@@ -608,6 +616,9 @@
       </c>
       <c r="P3" t="n">
         <v>0.3637789415331618</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>281</v>
       </c>
     </row>
     <row r="4">
@@ -642,10 +653,10 @@
         <v>-0.6184671711737429</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06144700679653801</v>
+        <v>0.07501155395072434</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>6.217248937900877e-15</v>
       </c>
       <c r="K4" t="n">
         <v>-0.4761710159545921</v>
@@ -664,6 +675,9 @@
       </c>
       <c r="P4" t="n">
         <v>0.3369701883695086</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>283</v>
       </c>
     </row>
     <row r="5">
@@ -698,10 +712,10 @@
         <v>-0.6038543099674142</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08660433020564759</v>
+        <v>0.07341976961093853</v>
       </c>
       <c r="J5" t="n">
-        <v>2.18360884929325e-11</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="K5" t="n">
         <v>-0.5142674666521265</v>
@@ -720,6 +734,9 @@
       </c>
       <c r="P5" t="n">
         <v>0.2774644207172029</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>284</v>
       </c>
     </row>
     <row r="6">
@@ -754,10 +771,10 @@
         <v>-0.5960227390393019</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1165329424726069</v>
+        <v>0.07467185297924157</v>
       </c>
       <c r="J6" t="n">
-        <v>5.804106248952223e-07</v>
+        <v>3.61932706027801e-14</v>
       </c>
       <c r="K6" t="n">
         <v>-0.5627852149503972</v>
@@ -776,6 +793,9 @@
       </c>
       <c r="P6" t="n">
         <v>0.2955499435836599</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>283</v>
       </c>
     </row>
     <row r="7">
@@ -810,10 +830,10 @@
         <v>-0.6214122143746015</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0593553884283942</v>
+        <v>0.07197738454306017</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>4.440892098500626e-16</v>
       </c>
       <c r="K7" t="n">
         <v>-0.5172082439313143</v>
@@ -832,6 +852,9 @@
       </c>
       <c r="P7" t="n">
         <v>0.2770951802582408</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>282</v>
       </c>
     </row>
     <row r="8">
@@ -866,7 +889,7 @@
         <v>-0.6308449359973219</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0656358092886765</v>
+        <v>0.05661657363507576</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -888,6 +911,9 @@
       </c>
       <c r="P8" t="n">
         <v>0.3009180083040703</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>283</v>
       </c>
     </row>
     <row r="9">
@@ -922,10 +948,10 @@
         <v>-0.6150393409074353</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08619240858568283</v>
+        <v>0.07511976413699162</v>
       </c>
       <c r="J9" t="n">
-        <v>7.997380535584853e-12</v>
+        <v>9.103828801926284e-15</v>
       </c>
       <c r="K9" t="n">
         <v>-0.5330989063196129</v>
@@ -944,6 +970,9 @@
       </c>
       <c r="P9" t="n">
         <v>0.2740896489927416</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>285</v>
       </c>
     </row>
   </sheetData>
